--- a/src/test/resources/testdata.xlsx
+++ b/src/test/resources/testdata.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sandesh Velhal\eclipse-workspace\Servicenow-AllModule\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vmalode\git\ServiceNowAllModule\ServiceNowAllModule\ServiceNowAllModule\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF77C7F6-DCC1-4AB7-A03A-0B4338125305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1B046E7-CF38-4216-925A-BBFF50B18C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" activeTab="3" xr2:uid="{47AEF9C5-A68B-4616-944B-F17818BC6EA4}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="3" xr2:uid="{47AEF9C5-A68B-4616-944B-F17818BC6EA4}"/>
   </bookViews>
   <sheets>
     <sheet name="ImpersonateUser" sheetId="2" r:id="rId1"/>
     <sheet name="Create_Inc" sheetId="1" r:id="rId2"/>
     <sheet name="Incident_Flow" sheetId="5" r:id="rId3"/>
     <sheet name="Problem" sheetId="3" r:id="rId4"/>
-    <sheet name="Normal_Change" sheetId="4" r:id="rId5"/>
-    <sheet name="Request" sheetId="6" r:id="rId6"/>
+    <sheet name="Knowledge" sheetId="7" r:id="rId5"/>
+    <sheet name="Normal_Change" sheetId="4" r:id="rId6"/>
+    <sheet name="Request" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="66">
   <si>
     <t>User</t>
   </si>
@@ -125,9 +126,6 @@
     <t>State</t>
   </si>
   <si>
-    <t>States</t>
-  </si>
-  <si>
     <t>New</t>
   </si>
   <si>
@@ -200,9 +198,6 @@
     <t>Beth Anglin</t>
   </si>
   <si>
-    <t>b</t>
-  </si>
-  <si>
     <t>2 - High</t>
   </si>
   <si>
@@ -213,6 +208,27 @@
   </si>
   <si>
     <t>Impersonate user</t>
+  </si>
+  <si>
+    <t>Knowledge base</t>
+  </si>
+  <si>
+    <t>Test VM</t>
+  </si>
+  <si>
+    <t>Known Error</t>
+  </si>
+  <si>
+    <t>Configuration item</t>
+  </si>
+  <si>
+    <t>JRun Server</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Test Description field details</t>
   </si>
 </sst>
 </file>
@@ -606,16 +622,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4232BF5-167B-438D-AD11-4378C7AE8B69}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -626,15 +642,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1455EC35-D54A-4DB2-8548-09D9706D20DE}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="28.875" customWidth="1"/>
-    <col min="3" max="3" width="14.5" customWidth="1"/>
-    <col min="4" max="4" width="12.375" customWidth="1"/>
+    <col min="2" max="2" width="28.90625" customWidth="1"/>
+    <col min="3" max="3" width="14.453125" customWidth="1"/>
+    <col min="4" max="4" width="12.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -642,13 +658,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" t="s">
         <v>45</v>
       </c>
-      <c r="D1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -662,7 +678,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -676,7 +692,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -698,13 +714,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{643766E5-CBFA-4DF2-9AD5-873E90561A67}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.375" customWidth="1"/>
-    <col min="2" max="2" width="22.75" customWidth="1"/>
+    <col min="1" max="1" width="13.36328125" customWidth="1"/>
+    <col min="2" max="2" width="22.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -712,25 +728,25 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" t="s">
         <v>45</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>46</v>
       </c>
-      <c r="E1" t="s">
-        <v>47</v>
-      </c>
       <c r="F1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" t="s">
         <v>36</v>
       </c>
-      <c r="G1" t="s">
-        <v>37</v>
-      </c>
       <c r="H1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -764,13 +780,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99DB1441-C323-479D-A628-08A5A45D8D8F}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.375" customWidth="1"/>
-    <col min="2" max="2" width="25.5" customWidth="1"/>
+    <col min="1" max="1" width="20.36328125" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>17</v>
       </c>
@@ -779,67 +795,71 @@
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:3" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:3" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-    </row>
-    <row r="4" spans="1:3" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
     </row>
-    <row r="5" spans="1:3" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:3" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:3" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="3" t="s">
         <v>21</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:3" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:3" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C9" s="1"/>
     </row>
-    <row r="10" spans="1:3" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="3" t="s">
         <v>24</v>
       </c>
@@ -848,7 +868,7 @@
       </c>
       <c r="C10" s="1"/>
     </row>
-    <row r="11" spans="1:3" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="3" t="s">
         <v>26</v>
       </c>
@@ -857,7 +877,7 @@
       </c>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="1:3" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
         <v>28</v>
       </c>
@@ -866,111 +886,113 @@
       </c>
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="1:3" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:3" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="1"/>
+    </row>
+    <row r="15" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-    </row>
-    <row r="15" spans="1:3" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:3" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
     </row>
-    <row r="18" spans="1:3" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:3" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
     </row>
-    <row r="20" spans="1:3" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
     </row>
-    <row r="21" spans="1:3" ht="28.55" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="3" t="s">
+    </row>
+    <row r="22" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="2" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
     </row>
-    <row r="23" spans="1:3" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
     </row>
-    <row r="24" spans="1:3" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
     </row>
-    <row r="25" spans="1:3" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
     </row>
-    <row r="26" spans="1:3" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
     </row>
-    <row r="27" spans="1:3" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -982,42 +1004,27 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B06AD26-2352-489D-A95B-22398751004B}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75136E97-D8F5-4F9A-ABE0-629640EA06C7}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="48.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1026,36 +1033,80 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B06AD26-2352-489D-A95B-22398751004B}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="29.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99F681A7-597C-4194-80FE-14F3FB1930FD}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" t="s">
         <v>50</v>
-      </c>
-      <c r="C1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D2" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>
